--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_datero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D2973C-113D-4CBB-BD6F-F8D1BD15D430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3336113E-D33F-4897-B2F4-7B56CBDA651D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="4200" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -817,13 +817,13 @@
         <v>112</v>
       </c>
       <c r="C2">
-        <v>3606.13</v>
+        <v>3557.47</v>
       </c>
       <c r="D2">
-        <v>2771.82</v>
+        <v>2721.54</v>
       </c>
       <c r="E2">
-        <v>2376.31</v>
+        <v>2323.6799999999998</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -834,13 +834,13 @@
         <v>112</v>
       </c>
       <c r="C3">
-        <v>4808.17</v>
+        <v>4743.29</v>
       </c>
       <c r="D3">
-        <v>3695.76</v>
+        <v>3628.72</v>
       </c>
       <c r="E3">
-        <v>3168.41</v>
+        <v>3098.24</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -851,13 +851,13 @@
         <v>112</v>
       </c>
       <c r="C4">
-        <v>6010.21</v>
+        <v>5929.11</v>
       </c>
       <c r="D4">
-        <v>4619.7</v>
+        <v>4535.91</v>
       </c>
       <c r="E4">
-        <v>3960.51</v>
+        <v>3872.8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -868,13 +868,13 @@
         <v>112</v>
       </c>
       <c r="C5">
-        <v>7212.25</v>
+        <v>7114.94</v>
       </c>
       <c r="D5">
-        <v>5543.64</v>
+        <v>5443.09</v>
       </c>
       <c r="E5">
-        <v>4752.62</v>
+        <v>4647.3599999999997</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -885,13 +885,13 @@
         <v>112</v>
       </c>
       <c r="C6">
-        <v>8414.2999999999993</v>
+        <v>8300.76</v>
       </c>
       <c r="D6">
-        <v>6467.58</v>
+        <v>6350.27</v>
       </c>
       <c r="E6">
-        <v>5544.72</v>
+        <v>5421.92</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -902,13 +902,13 @@
         <v>112</v>
       </c>
       <c r="C7">
-        <v>9616.64</v>
+        <v>9486.58</v>
       </c>
       <c r="D7" s="1">
-        <v>7391.51</v>
+        <v>7257.45</v>
       </c>
       <c r="E7">
-        <v>6336.82</v>
+        <v>6196.48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -919,13 +919,13 @@
         <v>112</v>
       </c>
       <c r="C8">
-        <v>10818.38</v>
+        <v>10672.41</v>
       </c>
       <c r="D8">
-        <v>8315.4500000000007</v>
+        <v>8164.63</v>
       </c>
       <c r="E8">
-        <v>7128.92</v>
+        <v>6971.04</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -936,13 +936,13 @@
         <v>114</v>
       </c>
       <c r="C9">
-        <v>12020.42</v>
+        <v>11858.23</v>
       </c>
       <c r="D9">
-        <v>9239.39</v>
+        <v>9071.81</v>
       </c>
       <c r="E9">
-        <v>7921.03</v>
+        <v>7745.6</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -953,13 +953,13 @@
         <v>115</v>
       </c>
       <c r="C10">
-        <v>13222.46</v>
+        <v>13044.05</v>
       </c>
       <c r="D10">
-        <v>10163.33</v>
+        <v>9978.99</v>
       </c>
       <c r="E10">
-        <v>8713.1299999999992</v>
+        <v>8520.16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -970,13 +970,13 @@
         <v>112</v>
       </c>
       <c r="C11">
-        <v>14424.51</v>
+        <v>14229.88</v>
       </c>
       <c r="D11">
-        <v>11087.27</v>
+        <v>10886.17</v>
       </c>
       <c r="E11">
-        <v>9505.23</v>
+        <v>9294.7199999999993</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -987,13 +987,13 @@
         <v>112</v>
       </c>
       <c r="C12">
-        <v>15626.55</v>
+        <v>15415.7</v>
       </c>
       <c r="D12">
-        <v>12011.21</v>
+        <v>11793.36</v>
       </c>
       <c r="E12">
-        <v>10297.33</v>
+        <v>10069.280000000001</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1004,13 +1004,13 @@
         <v>112</v>
       </c>
       <c r="C13">
-        <v>16828.59</v>
+        <v>16601.52</v>
       </c>
       <c r="D13">
-        <v>12935.15</v>
+        <v>12700.54</v>
       </c>
       <c r="E13">
-        <v>11089.44</v>
+        <v>10843.84</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1021,13 +1021,13 @@
         <v>116</v>
       </c>
       <c r="C14">
-        <v>19030.63</v>
+        <v>17787.34</v>
       </c>
       <c r="D14">
-        <v>13859.09</v>
+        <v>13607.72</v>
       </c>
       <c r="E14">
-        <v>11881.54</v>
+        <v>11618.4</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1038,13 +1038,13 @@
         <v>112</v>
       </c>
       <c r="C15">
-        <v>19232.68</v>
+        <v>18973.169999999998</v>
       </c>
       <c r="D15">
-        <v>14783.03</v>
+        <v>14514.9</v>
       </c>
       <c r="E15">
-        <v>12673.64</v>
+        <v>12392.96</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1055,13 +1055,13 @@
         <v>112</v>
       </c>
       <c r="C16">
-        <v>20434.72</v>
+        <v>20158.990000000002</v>
       </c>
       <c r="D16">
-        <v>15706.87</v>
+        <v>15422.08</v>
       </c>
       <c r="E16">
-        <v>13465.74</v>
+        <v>13167.52</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1072,13 +1072,13 @@
         <v>112</v>
       </c>
       <c r="C17">
-        <v>21636.76</v>
+        <v>21344.81</v>
       </c>
       <c r="D17">
-        <v>16630.91</v>
+        <v>16329.26</v>
       </c>
       <c r="E17">
-        <v>14257.85</v>
+        <v>13942.08</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1089,13 +1089,13 @@
         <v>112</v>
       </c>
       <c r="C18">
-        <v>22838.799999999999</v>
+        <v>22530.639999999999</v>
       </c>
       <c r="D18">
-        <v>17554.849999999999</v>
+        <v>17236.439999999999</v>
       </c>
       <c r="E18">
-        <v>15049.95</v>
+        <v>14716.64</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1106,13 +1106,13 @@
         <v>113</v>
       </c>
       <c r="C19">
-        <v>24040.84</v>
+        <v>23716.46</v>
       </c>
       <c r="D19">
-        <v>18478.79</v>
+        <v>18143.62</v>
       </c>
       <c r="E19">
-        <v>15842.05</v>
+        <v>15491.19</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1123,13 +1123,13 @@
         <v>112</v>
       </c>
       <c r="C20">
-        <v>25242.89</v>
+        <v>24902.28</v>
       </c>
       <c r="D20">
-        <v>19402.73</v>
+        <v>19050.8</v>
       </c>
       <c r="E20">
-        <v>16634.150000000001</v>
+        <v>16265.75</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1140,13 +1140,13 @@
         <v>112</v>
       </c>
       <c r="C21">
-        <v>26444.93</v>
+        <v>26088.1</v>
       </c>
       <c r="D21">
-        <v>20326.669999999998</v>
+        <v>19957.990000000002</v>
       </c>
       <c r="E21">
-        <v>17426.259999999998</v>
+        <v>17040.310000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1157,13 +1157,13 @@
         <v>112</v>
       </c>
       <c r="C22">
-        <v>27646.97</v>
+        <v>27273.93</v>
       </c>
       <c r="D22">
-        <v>21250.6</v>
+        <v>20865.169999999998</v>
       </c>
       <c r="E22">
-        <v>18218.36</v>
+        <v>17814.87</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1174,13 +1174,13 @@
         <v>112</v>
       </c>
       <c r="C23">
-        <v>28848.01</v>
+        <v>28459.75</v>
       </c>
       <c r="D23">
-        <v>22174.54</v>
+        <v>21772.35</v>
       </c>
       <c r="E23">
-        <v>19010.46</v>
+        <v>18589.43</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1191,13 +1191,13 @@
         <v>117</v>
       </c>
       <c r="C24">
-        <v>30051.06</v>
+        <v>29645.57</v>
       </c>
       <c r="D24">
-        <v>23098.48</v>
+        <v>22679.53</v>
       </c>
       <c r="E24">
-        <v>19802.560000000001</v>
+        <v>19363.990000000002</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1208,13 +1208,13 @@
         <v>112</v>
       </c>
       <c r="C25">
-        <v>31253.1</v>
+        <v>30831.4</v>
       </c>
       <c r="D25">
-        <v>24022.42</v>
+        <v>23586.71</v>
       </c>
       <c r="E25">
-        <v>20594.669999999998</v>
+        <v>20138.55</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1225,13 +1225,13 @@
         <v>112</v>
       </c>
       <c r="C26">
-        <v>32455.14</v>
+        <v>32017.22</v>
       </c>
       <c r="D26">
-        <v>24946.36</v>
+        <v>24493.89</v>
       </c>
       <c r="E26">
-        <v>21386.77</v>
+        <v>20913.11</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1242,13 +1242,13 @@
         <v>112</v>
       </c>
       <c r="C27">
-        <v>33657.18</v>
+        <v>33203.040000000001</v>
       </c>
       <c r="D27">
-        <v>25870.3</v>
+        <v>25401.07</v>
       </c>
       <c r="E27">
-        <v>22178.87</v>
+        <v>21687.67</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1259,13 +1259,13 @@
         <v>112</v>
       </c>
       <c r="C28">
-        <v>34859.22</v>
+        <v>34388.870000000003</v>
       </c>
       <c r="D28">
-        <v>26794.240000000002</v>
+        <v>26308.25</v>
       </c>
       <c r="E28">
-        <v>22970.98</v>
+        <v>22462.23</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1276,13 +1276,13 @@
         <v>118</v>
       </c>
       <c r="C29">
-        <v>36061.269999999997</v>
+        <v>35574.69</v>
       </c>
       <c r="D29">
-        <v>27718.18</v>
+        <v>27215.439999999999</v>
       </c>
       <c r="E29">
-        <v>23736.080000000002</v>
+        <v>23236.79</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1293,13 +1293,13 @@
         <v>112</v>
       </c>
       <c r="C30">
-        <v>37263.31</v>
+        <v>36760.51</v>
       </c>
       <c r="D30">
-        <v>28642.12</v>
+        <v>28122.62</v>
       </c>
       <c r="E30">
-        <v>24555.18</v>
+        <v>24011.35</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1310,13 +1310,13 @@
         <v>112</v>
       </c>
       <c r="C31">
-        <v>38465.35</v>
+        <v>37946.33</v>
       </c>
       <c r="D31">
-        <v>29566.06</v>
+        <v>29029.8</v>
       </c>
       <c r="E31">
-        <v>25347.279999999999</v>
+        <v>24785.91</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1327,13 +1327,13 @@
         <v>112</v>
       </c>
       <c r="C32">
-        <v>39667.39</v>
+        <v>39132.160000000003</v>
       </c>
       <c r="D32">
-        <v>30490</v>
+        <v>29936.98</v>
       </c>
       <c r="E32">
-        <v>26139.39</v>
+        <v>25560.47</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1344,13 +1344,13 @@
         <v>112</v>
       </c>
       <c r="C33">
-        <v>40869.440000000002</v>
+        <v>40317.980000000003</v>
       </c>
       <c r="D33">
-        <v>31413.94</v>
+        <v>30844.16</v>
       </c>
       <c r="E33">
-        <v>26931.49</v>
+        <v>26335.03</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1361,13 +1361,13 @@
         <v>119</v>
       </c>
       <c r="C34">
-        <v>42071.48</v>
+        <v>41503.800000000003</v>
       </c>
       <c r="D34">
-        <v>32337.88</v>
+        <v>31751.34</v>
       </c>
       <c r="E34">
-        <v>27723.59</v>
+        <v>27109.59</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1378,13 +1378,13 @@
         <v>112</v>
       </c>
       <c r="C35">
-        <v>43273.52</v>
+        <v>42689.63</v>
       </c>
       <c r="D35">
-        <v>33261.82</v>
+        <v>32658.52</v>
       </c>
       <c r="E35">
-        <v>28515.69</v>
+        <v>27884.15</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1395,13 +1395,13 @@
         <v>112</v>
       </c>
       <c r="C36">
-        <v>44475.56</v>
+        <v>43875.45</v>
       </c>
       <c r="D36">
-        <v>34185.760000000002</v>
+        <v>33565.699999999997</v>
       </c>
       <c r="E36">
-        <v>29307.8</v>
+        <v>28658.71</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1412,13 +1412,13 @@
         <v>112</v>
       </c>
       <c r="C37">
-        <v>45667.6</v>
+        <v>45061.27</v>
       </c>
       <c r="D37">
-        <v>35109.69</v>
+        <v>34472.879999999997</v>
       </c>
       <c r="E37">
-        <v>30099.9</v>
+        <v>29433.27</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1429,13 +1429,13 @@
         <v>112</v>
       </c>
       <c r="C38">
-        <v>46879.65</v>
+        <v>46247.09</v>
       </c>
       <c r="D38">
-        <v>36033.629999999997</v>
+        <v>35380.07</v>
       </c>
       <c r="E38">
-        <v>30892</v>
+        <v>30207.83</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1446,13 +1446,13 @@
         <v>120</v>
       </c>
       <c r="C39">
-        <v>48081.69</v>
+        <v>47432.92</v>
       </c>
       <c r="D39">
-        <v>36957.57</v>
+        <v>36287.25</v>
       </c>
       <c r="E39">
-        <v>31684.1</v>
+        <v>30982.39</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1463,13 +1463,13 @@
         <v>112</v>
       </c>
       <c r="C40">
-        <v>49283.73</v>
+        <v>48618.74</v>
       </c>
       <c r="D40">
-        <v>37881.51</v>
+        <v>37194.43</v>
       </c>
       <c r="E40">
-        <v>32476.21</v>
+        <v>31756.95</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1480,13 +1480,13 @@
         <v>112</v>
       </c>
       <c r="C41">
-        <v>50485.77</v>
+        <v>49804.56</v>
       </c>
       <c r="D41">
-        <v>38805.449999999997</v>
+        <v>38101.61</v>
       </c>
       <c r="E41">
-        <v>33268.31</v>
+        <v>32531.51</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1497,13 +1497,13 @@
         <v>112</v>
       </c>
       <c r="C42">
-        <v>51687.82</v>
+        <v>50990.39</v>
       </c>
       <c r="D42">
-        <v>39729.39</v>
+        <v>39008.79</v>
       </c>
       <c r="E42">
-        <v>34060.410000000003</v>
+        <v>33306.07</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1514,13 +1514,13 @@
         <v>112</v>
       </c>
       <c r="C43">
-        <v>52889.86</v>
+        <v>52176.21</v>
       </c>
       <c r="D43">
-        <v>40653.33</v>
+        <v>39915.97</v>
       </c>
       <c r="E43">
-        <v>34852.51</v>
+        <v>34080.629999999997</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1531,13 +1531,13 @@
         <v>121</v>
       </c>
       <c r="C44">
-        <v>54091.9</v>
+        <v>53362.03</v>
       </c>
       <c r="D44">
-        <v>41557.269999999997</v>
+        <v>40823.15</v>
       </c>
       <c r="E44">
-        <v>35644.620000000003</v>
+        <v>34855.19</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1548,13 +1548,13 @@
         <v>112</v>
       </c>
       <c r="C45">
-        <v>55293.94</v>
+        <v>54547.86</v>
       </c>
       <c r="D45">
-        <v>42501.21</v>
+        <v>41730.33</v>
       </c>
       <c r="E45">
-        <v>36436.720000000001</v>
+        <v>35629.75</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1565,13 +1565,13 @@
         <v>112</v>
       </c>
       <c r="C46">
-        <v>56495.98</v>
+        <v>55733.68</v>
       </c>
       <c r="D46">
-        <v>43425.15</v>
+        <v>42637.52</v>
       </c>
       <c r="E46">
-        <v>37228.82</v>
+        <v>36404.31</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1582,13 +1582,13 @@
         <v>112</v>
       </c>
       <c r="C47">
-        <v>57698.03</v>
+        <v>56919.5</v>
       </c>
       <c r="D47">
-        <v>44349.09</v>
+        <v>43544.7</v>
       </c>
       <c r="E47">
-        <v>38020.92</v>
+        <v>37178.870000000003</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1599,13 +1599,13 @@
         <v>112</v>
       </c>
       <c r="C48">
-        <v>59800.07</v>
+        <v>58105.32</v>
       </c>
       <c r="D48">
-        <v>45273.03</v>
+        <v>44451.88</v>
       </c>
       <c r="E48">
-        <v>38813.03</v>
+        <v>37953.43</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1616,13 +1616,13 @@
         <v>122</v>
       </c>
       <c r="C49">
-        <v>60102.11</v>
+        <v>59291.15</v>
       </c>
       <c r="D49">
-        <v>46196.97</v>
+        <v>45359.06</v>
       </c>
       <c r="E49">
-        <v>39605.129999999997</v>
+        <v>38727.99</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1633,13 +1633,13 @@
         <v>112</v>
       </c>
       <c r="C50">
-        <v>61304.15</v>
+        <v>60476.97</v>
       </c>
       <c r="D50">
-        <v>47120.91</v>
+        <v>46266.239999999998</v>
       </c>
       <c r="E50">
-        <v>40397.230000000003</v>
+        <v>39502.550000000003</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1650,13 +1650,13 @@
         <v>112</v>
       </c>
       <c r="C51">
-        <v>62506.2</v>
+        <v>61662.79</v>
       </c>
       <c r="D51">
-        <v>48044.85</v>
+        <v>47173.42</v>
       </c>
       <c r="E51">
-        <v>41189.33</v>
+        <v>40277.11</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1667,13 +1667,13 @@
         <v>112</v>
       </c>
       <c r="C52">
-        <v>63708.24</v>
+        <v>62848.62</v>
       </c>
       <c r="D52">
-        <v>48968.78</v>
+        <v>48080.6</v>
       </c>
       <c r="E52">
-        <v>41981.440000000002</v>
+        <v>41051.67</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1684,13 +1684,13 @@
         <v>112</v>
       </c>
       <c r="C53">
-        <v>64910.28</v>
+        <v>64034.44</v>
       </c>
       <c r="D53">
-        <v>49892.72</v>
+        <v>48987.78</v>
       </c>
       <c r="E53">
-        <v>42773.54</v>
+        <v>41826.230000000003</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1701,13 +1701,13 @@
         <v>112</v>
       </c>
       <c r="C54">
-        <v>66112.320000000007</v>
+        <v>65220.26</v>
       </c>
       <c r="D54">
-        <v>50816.66</v>
+        <v>49894.97</v>
       </c>
       <c r="E54">
-        <v>43565.64</v>
+        <v>42600.79</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1718,13 +1718,13 @@
         <v>112</v>
       </c>
       <c r="C55">
-        <v>67314.36</v>
+        <v>66406.09</v>
       </c>
       <c r="D55">
-        <v>51740.6</v>
+        <v>50802.15</v>
       </c>
       <c r="E55">
-        <v>44357.75</v>
+        <v>43375.35</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1735,13 +1735,13 @@
         <v>112</v>
       </c>
       <c r="C56">
-        <v>68516.41</v>
+        <v>67591.91</v>
       </c>
       <c r="D56">
-        <v>52664.54</v>
+        <v>51709.33</v>
       </c>
       <c r="E56">
-        <v>45149.85</v>
+        <v>44149.91</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1752,13 +1752,13 @@
         <v>112</v>
       </c>
       <c r="C57">
-        <v>69718.45</v>
+        <v>68777.73</v>
       </c>
       <c r="D57">
-        <v>53588.480000000003</v>
+        <v>52616.51</v>
       </c>
       <c r="E57">
-        <v>45941.95</v>
+        <v>44924.46</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1769,13 +1769,13 @@
         <v>112</v>
       </c>
       <c r="C58">
-        <v>70920.490000000005</v>
+        <v>69963.55</v>
       </c>
       <c r="D58">
-        <v>54512.42</v>
+        <v>53523.69</v>
       </c>
       <c r="E58">
-        <v>46734.05</v>
+        <v>45699.02</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1786,13 +1786,13 @@
         <v>112</v>
       </c>
       <c r="C59">
-        <v>72112.53</v>
+        <v>71149.38</v>
       </c>
       <c r="D59">
-        <v>55436.36</v>
+        <v>54430.87</v>
       </c>
       <c r="E59">
-        <v>47526.16</v>
+        <v>46473.58</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1803,13 +1803,13 @@
         <v>112</v>
       </c>
       <c r="C60">
-        <v>73324.58</v>
+        <v>72335.199999999997</v>
       </c>
       <c r="D60">
-        <v>56360.3</v>
+        <v>55338.05</v>
       </c>
       <c r="E60">
-        <v>48318.26</v>
+        <v>47248.14</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1820,13 +1820,13 @@
         <v>112</v>
       </c>
       <c r="C61">
-        <v>74526.62</v>
+        <v>73521.02</v>
       </c>
       <c r="D61">
-        <v>57284.24</v>
+        <v>56245.23</v>
       </c>
       <c r="E61">
-        <v>49110.36</v>
+        <v>48022.7</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1837,13 +1837,13 @@
         <v>112</v>
       </c>
       <c r="C62">
-        <v>75728.66</v>
+        <v>74706.850000000006</v>
       </c>
       <c r="D62">
-        <v>58208.18</v>
+        <v>57152.41</v>
       </c>
       <c r="E62">
-        <v>49902.46</v>
+        <v>48797.26</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1854,13 +1854,13 @@
         <v>112</v>
       </c>
       <c r="C63">
-        <v>76930.7</v>
+        <v>75892.67</v>
       </c>
       <c r="D63">
-        <v>59132.12</v>
+        <v>58059.6</v>
       </c>
       <c r="E63">
-        <v>50694.57</v>
+        <v>49571.82</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1871,13 +1871,13 @@
         <v>112</v>
       </c>
       <c r="C64">
-        <v>78132.740000000005</v>
+        <v>77078.490000000005</v>
       </c>
       <c r="D64">
-        <v>60056.06</v>
+        <v>58966.78</v>
       </c>
       <c r="E64">
-        <v>51486.67</v>
+        <v>50346.38</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -1888,13 +1888,13 @@
         <v>112</v>
       </c>
       <c r="C65">
-        <v>79334.789999999994</v>
+        <v>78264.31</v>
       </c>
       <c r="D65">
-        <v>60980</v>
+        <v>59873.96</v>
       </c>
       <c r="E65">
-        <v>52278.77</v>
+        <v>51120.94</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -1905,13 +1905,13 @@
         <v>112</v>
       </c>
       <c r="C66">
-        <v>80536.83</v>
+        <v>79450.14</v>
       </c>
       <c r="D66">
-        <v>61903.94</v>
+        <v>60781.14</v>
       </c>
       <c r="E66">
-        <v>53070.87</v>
+        <v>51895.5</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -1922,13 +1922,13 @@
         <v>112</v>
       </c>
       <c r="C67">
-        <v>81738.87</v>
+        <v>80635.960000000006</v>
       </c>
       <c r="D67">
-        <v>62827.87</v>
+        <v>61688.32</v>
       </c>
       <c r="E67">
-        <v>53862.98</v>
+        <v>52670.06</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -1939,13 +1939,13 @@
         <v>112</v>
       </c>
       <c r="C68">
-        <v>82940.91</v>
+        <v>81821.78</v>
       </c>
       <c r="D68">
-        <v>63751.81</v>
+        <v>62595.5</v>
       </c>
       <c r="E68">
-        <v>54655.08</v>
+        <v>53444.62</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -1956,13 +1956,13 @@
         <v>112</v>
       </c>
       <c r="C69">
-        <v>84142.96</v>
+        <v>83007.61</v>
       </c>
       <c r="D69">
-        <v>64675.75</v>
+        <v>63502.68</v>
       </c>
       <c r="E69">
-        <v>55447.18</v>
+        <v>54219.18</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -1973,13 +1973,13 @@
         <v>112</v>
       </c>
       <c r="C70">
-        <v>85345</v>
+        <v>84193.43</v>
       </c>
       <c r="D70">
-        <v>65599.69</v>
+        <v>64409.86</v>
       </c>
       <c r="E70">
-        <v>56239.28</v>
+        <v>54993.74</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -1990,13 +1990,13 @@
         <v>112</v>
       </c>
       <c r="C71">
-        <v>86547.04</v>
+        <v>85379.25</v>
       </c>
       <c r="D71">
-        <v>66523.63</v>
+        <v>65317.05</v>
       </c>
       <c r="E71">
-        <v>57031.39</v>
+        <v>55768.3</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2007,13 +2007,13 @@
         <v>112</v>
       </c>
       <c r="C72">
-        <v>87749.08</v>
+        <v>86565.08</v>
       </c>
       <c r="D72">
-        <v>67447.570000000007</v>
+        <v>66224.23</v>
       </c>
       <c r="E72">
-        <v>57823.49</v>
+        <v>56542.86</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2024,13 +2024,13 @@
         <v>112</v>
       </c>
       <c r="C73">
-        <v>88951.12</v>
+        <v>87750.9</v>
       </c>
       <c r="D73">
-        <v>68371.509999999995</v>
+        <v>67131.41</v>
       </c>
       <c r="E73">
-        <v>58615.59</v>
+        <v>57317.42</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2041,13 +2041,13 @@
         <v>112</v>
       </c>
       <c r="C74">
-        <v>90153.17</v>
+        <v>88936.72</v>
       </c>
       <c r="D74">
-        <v>69295.45</v>
+        <v>68038.59</v>
       </c>
       <c r="E74">
-        <v>59407.69</v>
+        <v>58091.98</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2058,13 +2058,13 @@
         <v>112</v>
       </c>
       <c r="C75">
-        <v>91355.21</v>
+        <v>90122.54</v>
       </c>
       <c r="D75">
-        <v>70219.39</v>
+        <v>68945.77</v>
       </c>
       <c r="E75">
-        <v>60199.8</v>
+        <v>58866.54</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2075,13 +2075,13 @@
         <v>112</v>
       </c>
       <c r="C76">
-        <v>92557.25</v>
+        <v>91308.37</v>
       </c>
       <c r="D76">
-        <v>71143.33</v>
+        <v>69852.95</v>
       </c>
       <c r="E76">
-        <v>60991.9</v>
+        <v>59641.1</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2092,13 +2092,13 @@
         <v>112</v>
       </c>
       <c r="C77">
-        <v>93759.29</v>
+        <v>92494.19</v>
       </c>
       <c r="D77">
-        <v>72067.27</v>
+        <v>70760.13</v>
       </c>
       <c r="E77">
-        <v>61784</v>
+        <v>60415.66</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2109,13 +2109,13 @@
         <v>112</v>
       </c>
       <c r="C78">
-        <v>94961.34</v>
+        <v>93680.01</v>
       </c>
       <c r="D78">
-        <v>72991.210000000006</v>
+        <v>71667.31</v>
       </c>
       <c r="E78">
-        <v>62576.1</v>
+        <v>61190.22</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2126,13 +2126,13 @@
         <v>112</v>
       </c>
       <c r="C79">
-        <v>96163.38</v>
+        <v>94865.84</v>
       </c>
       <c r="D79">
-        <v>73915.149999999994</v>
+        <v>72574.490000000005</v>
       </c>
       <c r="E79">
-        <v>63368.21</v>
+        <v>61964.78</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2143,13 +2143,13 @@
         <v>112</v>
       </c>
       <c r="C80">
-        <v>97365.42</v>
+        <v>96051.66</v>
       </c>
       <c r="D80">
-        <v>74839.09</v>
+        <v>73481.679999999993</v>
       </c>
       <c r="E80">
-        <v>64160.31</v>
+        <v>62739.34</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2160,13 +2160,13 @@
         <v>112</v>
       </c>
       <c r="C81">
-        <v>98567.46</v>
+        <v>97237.48</v>
       </c>
       <c r="D81">
-        <v>75763.03</v>
+        <v>74388.86</v>
       </c>
       <c r="E81">
-        <v>64952.41</v>
+        <v>63513.9</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2177,13 +2177,13 @@
         <v>112</v>
       </c>
       <c r="C82">
-        <v>99769.5</v>
+        <v>98423.3</v>
       </c>
       <c r="D82">
-        <v>76686.960000000006</v>
+        <v>75296.039999999994</v>
       </c>
       <c r="E82">
-        <v>65744.52</v>
+        <v>64288.46</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2194,13 +2194,13 @@
         <v>112</v>
       </c>
       <c r="C83">
-        <v>100971.55</v>
+        <v>99609.13</v>
       </c>
       <c r="D83">
-        <v>77610.899999999994</v>
+        <v>76203.22</v>
       </c>
       <c r="E83">
-        <v>66536.62</v>
+        <v>65063.02</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2211,13 +2211,13 @@
         <v>112</v>
       </c>
       <c r="C84">
-        <v>102173.59</v>
+        <v>100794.95</v>
       </c>
       <c r="D84">
-        <v>78534.84</v>
+        <v>77110.399999999994</v>
       </c>
       <c r="E84">
-        <v>67328.72</v>
+        <v>65837.58</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2228,13 +2228,13 @@
         <v>112</v>
       </c>
       <c r="C85">
-        <v>103375.63</v>
+        <v>101980.77</v>
       </c>
       <c r="D85">
-        <v>79458.78</v>
+        <v>78017.58</v>
       </c>
       <c r="E85">
-        <v>68120.820000000007</v>
+        <v>66612.14</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2245,13 +2245,13 @@
         <v>112</v>
       </c>
       <c r="C86">
-        <v>104577.67</v>
+        <v>103166.6</v>
       </c>
       <c r="D86">
-        <v>80382.720000000001</v>
+        <v>78924.759999999995</v>
       </c>
       <c r="E86">
-        <v>68912.929999999993</v>
+        <v>67386.7</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2262,13 +2262,13 @@
         <v>112</v>
       </c>
       <c r="C87">
-        <v>105779.72</v>
+        <v>104352.42</v>
       </c>
       <c r="D87">
-        <v>81306.66</v>
+        <v>79831.94</v>
       </c>
       <c r="E87">
-        <v>69705.03</v>
+        <v>68161.259999999995</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2279,13 +2279,13 @@
         <v>112</v>
       </c>
       <c r="C88">
-        <v>106981.75999999999</v>
+        <v>105538.24000000001</v>
       </c>
       <c r="D88">
-        <v>82230.600000000006</v>
+        <v>80739.13</v>
       </c>
       <c r="E88">
-        <v>70497.13</v>
+        <v>68935.820000000007</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2296,13 +2296,13 @@
         <v>112</v>
       </c>
       <c r="C89">
-        <v>108183.8</v>
+        <v>106724.07</v>
       </c>
       <c r="D89">
-        <v>83154.539999999994</v>
+        <v>81646.31</v>
       </c>
       <c r="E89">
-        <v>71289.23</v>
+        <v>69710.38</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2313,13 +2313,13 @@
         <v>112</v>
       </c>
       <c r="C90">
-        <v>109385.84</v>
+        <v>107909.89</v>
       </c>
       <c r="D90">
-        <v>84078.48</v>
+        <v>82553.490000000005</v>
       </c>
       <c r="E90">
-        <v>72081.34</v>
+        <v>70484.94</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2330,13 +2330,13 @@
         <v>112</v>
       </c>
       <c r="C91">
-        <v>110587.88</v>
+        <v>109095.71</v>
       </c>
       <c r="D91">
-        <v>85002.42</v>
+        <v>83460.67</v>
       </c>
       <c r="E91">
-        <v>72873.440000000002</v>
+        <v>71259.5</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2347,13 +2347,13 @@
         <v>112</v>
       </c>
       <c r="C92">
-        <v>111789.93</v>
+        <v>110281.53</v>
       </c>
       <c r="D92">
-        <v>85926.36</v>
+        <v>84367.85</v>
       </c>
       <c r="E92">
-        <v>73665.539999999994</v>
+        <v>72034.06</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2364,13 +2364,13 @@
         <v>112</v>
       </c>
       <c r="C93">
-        <v>112991.97</v>
+        <v>111467.36</v>
       </c>
       <c r="D93">
-        <v>86850.3</v>
+        <v>85275.03</v>
       </c>
       <c r="E93">
-        <v>74457.64</v>
+        <v>72808.62</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2381,13 +2381,13 @@
         <v>112</v>
       </c>
       <c r="C94">
-        <v>114194.01</v>
+        <v>112653.18</v>
       </c>
       <c r="D94">
-        <v>87774.24</v>
+        <v>86182.21</v>
       </c>
       <c r="E94">
-        <v>75249.75</v>
+        <v>73583.179999999993</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2398,13 +2398,13 @@
         <v>112</v>
       </c>
       <c r="C95">
-        <v>115396.05</v>
+        <v>113839</v>
       </c>
       <c r="D95">
-        <v>88698.18</v>
+        <v>87089.39</v>
       </c>
       <c r="E95">
-        <v>76041.850000000006</v>
+        <v>74357.73</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2415,13 +2415,13 @@
         <v>112</v>
       </c>
       <c r="C96">
-        <v>116598.1</v>
+        <v>115024.83</v>
       </c>
       <c r="D96">
-        <v>89622.12</v>
+        <v>87996.57</v>
       </c>
       <c r="E96">
-        <v>76833.95</v>
+        <v>75132.289999999994</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2432,13 +2432,13 @@
         <v>112</v>
       </c>
       <c r="C97">
-        <v>117800.14</v>
+        <v>116210.65</v>
       </c>
       <c r="D97">
-        <v>90546.05</v>
+        <v>88903.76</v>
       </c>
       <c r="E97">
-        <v>77626.05</v>
+        <v>75906.850000000006</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2449,13 +2449,13 @@
         <v>112</v>
       </c>
       <c r="C98">
-        <v>119002.18</v>
+        <v>117396.47</v>
       </c>
       <c r="D98">
-        <v>91469.99</v>
+        <v>89810.94</v>
       </c>
       <c r="E98">
-        <v>78418.16</v>
+        <v>76681.41</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2466,13 +2466,13 @@
         <v>112</v>
       </c>
       <c r="C99">
-        <v>120204.22</v>
+        <v>118582.29</v>
       </c>
       <c r="D99">
-        <v>92393.93</v>
+        <v>90718.12</v>
       </c>
       <c r="E99">
-        <v>79210.259999999995</v>
+        <v>77455.97</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2483,13 +2483,13 @@
         <v>112</v>
       </c>
       <c r="C100">
-        <v>126214.43</v>
+        <v>124511.41</v>
       </c>
       <c r="D100">
-        <v>97013.63</v>
+        <v>95254.02</v>
       </c>
       <c r="E100">
-        <v>83170.77</v>
+        <v>81328.77</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2500,13 +2500,13 @@
         <v>112</v>
       </c>
       <c r="C101">
-        <v>132224.64000000001</v>
+        <v>130440.52</v>
       </c>
       <c r="D101">
-        <v>101633.33</v>
+        <v>99789.93</v>
       </c>
       <c r="E101">
-        <v>87131.29</v>
+        <v>85201.57</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2517,13 +2517,13 @@
         <v>112</v>
       </c>
       <c r="C102">
-        <v>138234.85999999999</v>
+        <v>136369.64000000001</v>
       </c>
       <c r="D102">
-        <v>106253.02</v>
+        <v>104325.84</v>
       </c>
       <c r="E102">
-        <v>91091.8</v>
+        <v>89074.37</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2534,13 +2534,13 @@
         <v>112</v>
       </c>
       <c r="C103">
-        <v>144245.07</v>
+        <v>142298.75</v>
       </c>
       <c r="D103">
-        <v>110872.72</v>
+        <v>108861.74</v>
       </c>
       <c r="E103">
-        <v>95052.31</v>
+        <v>92947.17</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2551,13 +2551,13 @@
         <v>112</v>
       </c>
       <c r="C104">
-        <v>150255.28</v>
+        <v>148227.87</v>
       </c>
       <c r="D104">
-        <v>115492.42</v>
+        <v>113397.65</v>
       </c>
       <c r="E104">
-        <v>99012.82</v>
+        <v>96819.97</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2568,13 +2568,13 @@
         <v>112</v>
       </c>
       <c r="C105">
-        <v>156265.49</v>
+        <v>154156.98000000001</v>
       </c>
       <c r="D105">
-        <v>120112.11</v>
+        <v>117933.55</v>
       </c>
       <c r="E105">
-        <v>102973.34</v>
+        <v>100692.77</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2585,13 +2585,13 @@
         <v>112</v>
       </c>
       <c r="C106">
-        <v>162275.70000000001</v>
+        <v>160086.1</v>
       </c>
       <c r="D106">
-        <v>124731.81</v>
+        <v>122469.46</v>
       </c>
       <c r="E106">
-        <v>106933.85</v>
+        <v>104565.56</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2602,13 +2602,13 @@
         <v>112</v>
       </c>
       <c r="C107">
-        <v>168285.91</v>
+        <v>166015.21</v>
       </c>
       <c r="D107">
-        <v>129351.51</v>
+        <v>127005.37</v>
       </c>
       <c r="E107">
-        <v>110894.36</v>
+        <v>108438.36</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2619,13 +2619,13 @@
         <v>112</v>
       </c>
       <c r="C108">
-        <v>174296.12</v>
+        <v>171944.33</v>
       </c>
       <c r="D108">
-        <v>133971.20000000001</v>
+        <v>131541.26999999999</v>
       </c>
       <c r="E108">
-        <v>114854.88</v>
+        <v>112311.16</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2636,13 +2636,13 @@
         <v>112</v>
       </c>
       <c r="C109">
-        <v>180306.33</v>
+        <v>177873.44</v>
       </c>
       <c r="D109">
-        <v>138590.9</v>
+        <v>136077.18</v>
       </c>
       <c r="E109">
-        <v>118815.39</v>
+        <v>116183.96</v>
       </c>
     </row>
   </sheetData>
